--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487044_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487044_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.325</v>
+        <v>6.4832</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3044</v>
+        <v>4.4626</v>
       </c>
       <c r="F2" t="n">
         <v>2.0206</v>
@@ -610,10 +610,10 @@
         <v>2.7021</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1667</v>
+        <v>1.325</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4212</v>
+        <v>0.5794</v>
       </c>
       <c r="U2" t="n">
         <v>0.7456</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.986</v>
+        <v>4.9999</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6777</v>
+        <v>4.4774</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3083</v>
+        <v>0.5225</v>
       </c>
       <c r="G3" t="n">
         <v>5.013</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.78</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6808</v>
+        <v>0.4806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.3133</v>
       </c>
       <c r="V3" t="n">
         <v>-0.614</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6675</v>
+        <v>4.8692</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5779</v>
+        <v>2.5386</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0896</v>
+        <v>2.3305</v>
       </c>
       <c r="G4" t="n">
         <v>1.8945</v>
@@ -766,13 +766,13 @@
         <v>2.5091</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.5308</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9518</v>
+        <v>0.0089</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2809</v>
+        <v>0.5218</v>
       </c>
       <c r="V4" t="n">
         <v>0.8999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3568</v>
+        <v>2.0157</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5432</v>
+        <v>1.1481</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>0.8675</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3257</v>
+        <v>1.7262</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2636</v>
+        <v>1.332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0621</v>
+        <v>0.3941</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3852</v>
+        <v>1.3454</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3038</v>
+        <v>1.3454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0596</v>
+        <v>0.3807</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0403</v>
+        <v>-0.0134</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0193</v>
+        <v>0.3941</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8032</v>
+        <v>0.1894</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6808</v>
+        <v>-0.1973</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1223</v>
+        <v>0.3867</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.862</v>
+        <v>1.5339</v>
       </c>
       <c r="E6" t="n">
-        <v>1.048</v>
+        <v>-0.8843</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.4181</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7262</v>
+        <v>1.3257</v>
       </c>
       <c r="H6" t="n">
-        <v>1.332</v>
+        <v>1.2636</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3941</v>
+        <v>0.0621</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3454</v>
+        <v>1.3852</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3454</v>
+        <v>1.3038</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0814</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3807</v>
+        <v>-0.0596</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0134</v>
+        <v>-0.0403</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3941</v>
+        <v>-0.0193</v>
       </c>
       <c r="P6" t="n">
-        <v>0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R6" t="n">
-        <v>0.386</v>
+        <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0357</v>
+        <v>0.9802</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2974</v>
+        <v>0.3398</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3331</v>
+        <v>0.6405</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2859</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>G. CHIA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8492</v>
+        <v>0.9415</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1213</v>
+        <v>-0.6631</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9705</v>
+        <v>1.6047</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9541</v>
+        <v>0.2029</v>
       </c>
       <c r="H7" t="n">
-        <v>1.123</v>
+        <v>-0.0641</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8311</v>
+        <v>0.267</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2148</v>
+        <v>-0.5848</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3183</v>
+        <v>0.0828</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8964</v>
+        <v>-0.6676</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2607</v>
+        <v>0.7877</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1953</v>
+        <v>-0.1469</v>
       </c>
       <c r="O7" t="n">
         <v>0.9346</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.7021</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.158</v>
+        <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.497</v>
+        <v>0.1596</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4759</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9729</v>
+        <v>0.238</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. CHIA SANCHEZ</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7343</v>
+        <v>0.9354</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7633</v>
+        <v>0.1791</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4976</v>
+        <v>0.7563</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2029</v>
+        <v>3.9541</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0641</v>
+        <v>1.123</v>
       </c>
       <c r="I8" t="n">
-        <v>0.267</v>
+        <v>2.8311</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5848</v>
+        <v>4.2148</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0828</v>
+        <v>2.3183</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6676</v>
+        <v>1.8964</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7877</v>
+        <v>-0.2607</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1469</v>
+        <v>-1.1953</v>
       </c>
       <c r="O8" t="n">
         <v>0.9346</v>
       </c>
       <c r="P8" t="n">
-        <v>0.579</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R8" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0476</v>
+        <v>0.5833</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1785</v>
+        <v>-0.1755</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1309</v>
+        <v>0.7588</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3944</v>
+        <v>-0.7146</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1865</v>
+        <v>-0.2141</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5809</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0.1615</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4092</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4891</v>
+        <v>0.0886</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2261</v>
+        <v>-1.8874</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6559</v>
+        <v>-2.1566</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4298</v>
+        <v>0.2692</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8451</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>1.051</v>
+        <v>0.3897</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7403</v>
+        <v>0.2396</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3106</v>
+        <v>0.15</v>
       </c>
       <c r="V10" t="n">
         <v>1.2702</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8837</v>
+        <v>-3.0304</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4711</v>
+        <v>-3.6714</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5874</v>
+        <v>0.641</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4248</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4363</v>
+        <v>0.2895</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0132</v>
+        <v>-0.187</v>
       </c>
       <c r="U11" t="n">
-        <v>0.423</v>
+        <v>0.4766</v>
       </c>
       <c r="V11" t="n">
         <v>1.228</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7823</v>
+        <v>-3.0546</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0552</v>
+        <v>-5.4301</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7271</v>
+        <v>2.3755</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4743</v>
+        <v>-4.6027</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4408</v>
+        <v>-3.0118</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0335</v>
+        <v>-1.5908</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6737</v>
+        <v>-4.0953</v>
       </c>
       <c r="K12" t="n">
-        <v>0.207</v>
+        <v>-1.4492</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8807</v>
+        <v>-2.6461</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8006</v>
+        <v>-0.5074</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6478</v>
+        <v>-1.5627</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1528</v>
+        <v>1.0553</v>
       </c>
       <c r="P12" t="n">
-        <v>0.193</v>
+        <v>1.158</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.273</v>
+        <v>0.39</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4164</v>
+        <v>-0.3698</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1434</v>
+        <v>0.7598</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8419</v>
+        <v>-3.1418</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1906</v>
+        <v>-2.495</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3487</v>
+        <v>-0.6468</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6027</v>
+        <v>-2.4743</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.0118</v>
+        <v>-0.4408</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5908</v>
+        <v>-2.0335</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.0953</v>
+        <v>-1.6737</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4492</v>
+        <v>0.207</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6461</v>
+        <v>-1.8807</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5074</v>
+        <v>-0.8006</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5627</v>
+        <v>-0.6478</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0553</v>
+        <v>-0.1528</v>
       </c>
       <c r="P13" t="n">
-        <v>1.158</v>
+        <v>0.193</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.965</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3973</v>
+        <v>0.3675</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1303</v>
+        <v>0.1438</v>
       </c>
       <c r="U13" t="n">
-        <v>0.733</v>
+        <v>0.2237</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.652400000000004</v>
+        <v>9.950000000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.006100000000001</v>
+        <v>-2.708799999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>12.6585</v>
+        <v>12.6586</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4753</v>
+        <v>6.475300000000004</v>
       </c>
       <c r="H14" t="n">
-        <v>2.437499999999997</v>
+        <v>2.4375</v>
       </c>
       <c r="I14" t="n">
         <v>4.037800000000001</v>
@@ -1528,7 +1528,7 @@
         <v>-2.5096</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.5051</v>
+        <v>-4.505100000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-11.0525</v>
@@ -1546,13 +1546,13 @@
         <v>16.4055</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7903</v>
+        <v>6.0878</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.8728</v>
       </c>
       <c r="U14" t="n">
-        <v>5.214799999999999</v>
+        <v>5.215100000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.212300000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0319</v>
+        <v>2.5979</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2834</v>
+        <v>1.5541</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7485</v>
+        <v>1.0438</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9067</v>
+        <v>0.3794</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7047</v>
+        <v>1.9603</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2021</v>
+        <v>-1.5808</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4007</v>
+        <v>1.4273</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9869</v>
+        <v>3.3894</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.9621</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.494</v>
+        <v>-1.0479</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2822</v>
+        <v>-1.4292</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7883</v>
+        <v>0.3813</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2995</v>
+        <v>-0.8467</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4032</v>
+        <v>-0.9082</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7027</v>
+        <v>0.0614</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4905</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7763</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0367</v>
+        <v>1.9819</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1536</v>
+        <v>0.983</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8832</v>
+        <v>0.9989</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3794</v>
+        <v>0.9067</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9603</v>
+        <v>0.7047</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5808</v>
+        <v>0.2021</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4273</v>
+        <v>1.4007</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3894</v>
+        <v>1.9869</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9621</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0479</v>
+        <v>-0.494</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4292</v>
+        <v>-1.2822</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3813</v>
+        <v>0.7883</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1231</v>
+        <v>2.3161</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4079</v>
+        <v>0.2495</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3087</v>
+        <v>-0.7036</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0992</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>-1.4905</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2859</v>
+        <v>-1.7763</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3558</v>
+        <v>1.3488</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5059</v>
+        <v>-0.4058</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8617</v>
+        <v>1.7546</v>
       </c>
       <c r="G17" t="n">
         <v>0.2836</v>
@@ -1780,13 +1780,13 @@
         <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1071</v>
+        <v>0.1001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4164</v>
+        <v>-0.3163</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5235</v>
+        <v>0.4164</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7631</v>
+        <v>1.1447</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4554</v>
+        <v>-0.1747</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2185</v>
+        <v>1.3195</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3533</v>
+        <v>1.4172</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7017</v>
+        <v>-0.3621</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3484</v>
+        <v>1.7793</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8605</v>
+        <v>2.5852</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2743</v>
+        <v>0.7866</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.7986</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5072</v>
+        <v>-1.168</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4274</v>
+        <v>-1.1487</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9346</v>
+        <v>-0.0193</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9301</v>
+        <v>2.5091</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8137</v>
+        <v>-0.9171</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5949</v>
+        <v>-0.8298</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2188</v>
+        <v>-0.0873</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6302</v>
+        <v>0.9902</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4751</v>
+        <v>-1.2551</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1053</v>
+        <v>2.2453</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4172</v>
+        <v>-0.3533</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3621</v>
+        <v>-0.7017</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7793</v>
+        <v>0.3484</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5852</v>
+        <v>-0.8605</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7866</v>
+        <v>-0.2743</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7986</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.168</v>
+        <v>0.5072</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1487</v>
+        <v>-0.4274</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0193</v>
+        <v>0.9346</v>
       </c>
       <c r="P19" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4317</v>
+        <v>-0.5866</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1303</v>
+        <v>-0.3946</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3014</v>
+        <v>-0.192</v>
       </c>
       <c r="V19" t="n">
-        <v>0.06560000000000001</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.06560000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5825</v>
+        <v>-0.0183</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7441</v>
+        <v>0.1432</v>
       </c>
       <c r="F20" t="n">
         <v>-0.1616</v>
@@ -2014,10 +2014,10 @@
         <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.119</v>
+        <v>-0.7198</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5619</v>
+        <v>-0.039</v>
       </c>
       <c r="U20" t="n">
         <v>-0.6808</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6691</v>
+        <v>-1.9626</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4139</v>
+        <v>-1.8145</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2552</v>
+        <v>-0.1481</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7262</v>
@@ -2092,13 +2092,13 @@
         <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.078</v>
+        <v>-0.3715</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0462</v>
+        <v>-0.4468</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0317</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2859</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>R. NUÑEZ HERRERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8189</v>
+        <v>-2.1842</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1435</v>
+        <v>-1.7438</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6754</v>
+        <v>-0.4404</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.762</v>
+        <v>-2.1222</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9481000000000001</v>
+        <v>0.7938</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-2.916</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6676</v>
+        <v>-0.8807</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6676</v>
+        <v>2.4166</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-3.2973</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0944</v>
+        <v>-1.2415</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2805</v>
+        <v>-1.6227</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.3813</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.772</v>
+        <v>-0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7151999999999999</v>
+        <v>-1.0275</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4891</v>
+        <v>-0.7327</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2261</v>
+        <v>-0.2948</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9655</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.8342000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. NUÑEZ HERRERO</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1773</v>
+        <v>-2.3265</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8439</v>
+        <v>-1.5441</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3334</v>
+        <v>-0.7825</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1222</v>
+        <v>-1.762</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7938</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.916</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8807</v>
+        <v>-0.6676</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4166</v>
+        <v>-0.6676</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.2973</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2415</v>
+        <v>-1.0944</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6227</v>
+        <v>-0.2805</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3813</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>-0.772</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0206</v>
+        <v>0.2076</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8328</v>
+        <v>0.0886</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1877</v>
+        <v>0.119</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9655</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8342000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.564</v>
+        <v>-2.45</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8946</v>
+        <v>-0.9948</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6694</v>
+        <v>-1.4553</v>
       </c>
       <c r="G24" t="n">
         <v>-2.116</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3781</v>
+        <v>-0.2641</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0132</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3913</v>
+        <v>-0.1772</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7378</v>
+        <v>-3.357</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9122</v>
+        <v>-3.6118</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1744</v>
+        <v>0.2547</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2066</v>
@@ -2404,13 +2404,13 @@
         <v>2.3161</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.045</v>
+        <v>-0.6643</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8923</v>
+        <v>-0.5919</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1527</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>0.2859</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.0855</v>
+        <v>-5.4172</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.195</v>
+        <v>-3.7944</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8905</v>
+        <v>-1.6228</v>
       </c>
       <c r="G26" t="n">
         <v>-1.954</v>
@@ -2482,13 +2482,13 @@
         <v>1.5441</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6181</v>
+        <v>-0.9498</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6544</v>
+        <v>-0.2538</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9637</v>
+        <v>-0.696</v>
       </c>
       <c r="V26" t="n">
         <v>-1.1623</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.6524</v>
+        <v>-9.6523</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.6584</v>
+        <v>-12.6587</v>
       </c>
       <c r="F27" t="n">
         <v>3.006099999999999</v>
@@ -2527,19 +2527,19 @@
         <v>-6.475099999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.4374</v>
+        <v>-2.437399999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-4.0379</v>
       </c>
       <c r="J27" t="n">
-        <v>4.504999999999999</v>
+        <v>4.505</v>
       </c>
       <c r="K27" t="n">
         <v>11.0525</v>
       </c>
       <c r="L27" t="n">
-        <v>-6.5474</v>
+        <v>-6.547400000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-10.9803</v>
@@ -2551,7 +2551,7 @@
         <v>2.5096</v>
       </c>
       <c r="P27" t="n">
-        <v>4.825199999999998</v>
+        <v>4.8252</v>
       </c>
       <c r="Q27" t="n">
         <v>-16.4056</v>
@@ -2560,13 +2560,13 @@
         <v>21.2309</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.7903</v>
+        <v>-5.7902</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.215</v>
+        <v>-5.215000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.575</v>
+        <v>-0.5753000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-2.2123</v>
